--- a/portfolio_holdings.xlsx
+++ b/portfolio_holdings.xlsx
@@ -49,91 +49,91 @@
     <t>WEIGHTED AVG RATE</t>
   </si>
   <si>
+    <t>HDFCAMC</t>
+  </si>
+  <si>
+    <t>AUROPHARMA</t>
+  </si>
+  <si>
+    <t>POONAWALLA</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>HCG</t>
+  </si>
+  <si>
+    <t>OFSS</t>
+  </si>
+  <si>
+    <t>BSE</t>
+  </si>
+  <si>
+    <t>IRBINVIT</t>
+  </si>
+  <si>
+    <t>MOTHERSON</t>
+  </si>
+  <si>
+    <t>NUVAMA</t>
+  </si>
+  <si>
+    <t>PGINVIT</t>
+  </si>
+  <si>
+    <t>THYROCARE</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>BDL</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>HDBFS</t>
+  </si>
+  <si>
+    <t>NSDL</t>
+  </si>
+  <si>
+    <t>TANLA</t>
+  </si>
+  <si>
     <t>ALEMBICLTD</t>
   </si>
   <si>
+    <t>IDFCFIRSTB</t>
+  </si>
+  <si>
     <t>AMBUJACEM</t>
   </si>
   <si>
-    <t>AUROPHARMA</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>BDL</t>
-  </si>
-  <si>
-    <t>BSE</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
+    <t>TATAINVEST</t>
   </si>
   <si>
     <t>DABUR</t>
   </si>
   <si>
-    <t>HAL</t>
-  </si>
-  <si>
-    <t>HCG</t>
-  </si>
-  <si>
-    <t>HDBFS</t>
-  </si>
-  <si>
-    <t>HDFCAMC</t>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>RECLTD</t>
   </si>
   <si>
     <t>HDFCBANK</t>
   </si>
   <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>IDFCFIRSTB</t>
-  </si>
-  <si>
-    <t>IRBINVIT</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>MOTHERSON</t>
-  </si>
-  <si>
-    <t>NSDL</t>
-  </si>
-  <si>
-    <t>NUVAMA</t>
-  </si>
-  <si>
-    <t>OFSS</t>
-  </si>
-  <si>
-    <t>PGINVIT</t>
-  </si>
-  <si>
-    <t>POONAWALLA</t>
+    <t>SUZLON</t>
   </si>
   <si>
     <t>PROTEAN</t>
-  </si>
-  <si>
-    <t>RECLTD</t>
-  </si>
-  <si>
-    <t>SUZLON</t>
-  </si>
-  <si>
-    <t>TANLA</t>
-  </si>
-  <si>
-    <t>TATAINVEST</t>
-  </si>
-  <si>
-    <t>THYROCARE</t>
   </si>
   <si>
     <t>VEDL</t>
@@ -252,37 +252,37 @@
         <v>12</v>
       </c>
       <c r="B2" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3">
-        <v>91.3</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3">
-        <v>74.9</v>
+        <v>1783.43</v>
       </c>
       <c r="E2" s="3">
-        <v>75.39</v>
+        <v>2340.5</v>
       </c>
       <c r="F2" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="G2" s="3">
+        <v>-262.08</v>
+      </c>
+      <c r="H2" s="3">
         <v>0</v>
       </c>
-      <c r="G2" s="3">
-        <v>-143.19000000000005</v>
-      </c>
-      <c r="H2" s="3">
-        <v>-17.426067907995627</v>
-      </c>
       <c r="I2" s="3">
-        <v>821.6999999999999</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3">
-        <v>678.51</v>
+        <v>0</v>
       </c>
       <c r="K2" s="3">
-        <v>0</v>
+        <v>211.2</v>
       </c>
       <c r="L2" s="3">
-        <v>91.3022</v>
+        <v>2566.985</v>
       </c>
     </row>
     <row r="3">
@@ -290,37 +290,37 @@
         <v>13</v>
       </c>
       <c r="B3" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3">
-        <v>434.6</v>
+        <v>1060.43</v>
       </c>
       <c r="D3" s="3">
-        <v>394</v>
+        <v>1010</v>
       </c>
       <c r="E3" s="3">
-        <v>408.85</v>
+        <v>1342.1</v>
       </c>
       <c r="F3" s="3">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="G3" s="3">
-        <v>-334.75</v>
+        <v>281.66999999999985</v>
       </c>
       <c r="H3" s="3">
-        <v>-5.9249884951679705</v>
+        <v>26.561866412681635</v>
       </c>
       <c r="I3" s="3">
-        <v>5649.8</v>
+        <v>1060.43</v>
       </c>
       <c r="J3" s="3">
-        <v>5315.05</v>
+        <v>1342.1</v>
       </c>
       <c r="K3" s="3">
-        <v>0</v>
+        <v>37.69999999999982</v>
       </c>
       <c r="L3" s="3">
-        <v>434.5992</v>
+        <v>881.14</v>
       </c>
     </row>
     <row r="4">
@@ -331,34 +331,34 @@
         <v>1</v>
       </c>
       <c r="C4" s="3">
-        <v>1060.43</v>
+        <v>290.34</v>
       </c>
       <c r="D4" s="3">
-        <v>1010</v>
+        <v>318</v>
       </c>
       <c r="E4" s="3">
-        <v>1314.2</v>
+        <v>382.65</v>
       </c>
       <c r="F4" s="3">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="G4" s="3">
-        <v>253.76999999999998</v>
+        <v>92.31</v>
       </c>
       <c r="H4" s="3">
-        <v>23.93085823675301</v>
+        <v>31.793759041124204</v>
       </c>
       <c r="I4" s="3">
-        <v>1060.43</v>
+        <v>290.34</v>
       </c>
       <c r="J4" s="3">
-        <v>1314.2</v>
+        <v>382.65</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>14.25</v>
       </c>
       <c r="L4" s="3">
-        <v>881.14</v>
+        <v>83.73</v>
       </c>
     </row>
     <row r="5">
@@ -366,37 +366,37 @@
         <v>15</v>
       </c>
       <c r="B5" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3">
-        <v>1862.35</v>
+        <v>385.14</v>
       </c>
       <c r="D5" s="3">
-        <v>1662.7</v>
+        <v>356</v>
       </c>
       <c r="E5" s="3">
-        <v>1694.7</v>
+        <v>449.4</v>
       </c>
       <c r="F5" s="3">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="G5" s="3">
-        <v>-1173.550000000001</v>
+        <v>128.51999999999998</v>
       </c>
       <c r="H5" s="3">
-        <v>-9.002067280586365</v>
+        <v>16.68484187568157</v>
       </c>
       <c r="I5" s="3">
-        <v>13036.449999999999</v>
+        <v>770.28</v>
       </c>
       <c r="J5" s="3">
-        <v>11862.9</v>
+        <v>898.8</v>
       </c>
       <c r="K5" s="3">
-        <v>0</v>
+        <v>-2.1000000000000227</v>
       </c>
       <c r="L5" s="3">
-        <v>1857.9286</v>
+        <v>385.14</v>
       </c>
     </row>
     <row r="6">
@@ -404,37 +404,37 @@
         <v>16</v>
       </c>
       <c r="B6" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3">
-        <v>1394.66</v>
+        <v>4138.05</v>
       </c>
       <c r="D6" s="3">
-        <v>1131.2</v>
+        <v>3479.1</v>
       </c>
       <c r="E6" s="3">
-        <v>1136.9</v>
+        <v>3670.8</v>
       </c>
       <c r="F6" s="3">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="G6" s="3">
-        <v>-2319.84</v>
+        <v>-934.5</v>
       </c>
       <c r="H6" s="3">
-        <v>-18.481923909770124</v>
+        <v>-11.291550367926922</v>
       </c>
       <c r="I6" s="3">
-        <v>12551.94</v>
+        <v>8276.1</v>
       </c>
       <c r="J6" s="3">
-        <v>10232.1</v>
+        <v>7341.6</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>367.2000000000007</v>
       </c>
       <c r="L6" s="3">
-        <v>1394.6589</v>
+        <v>4145.735</v>
       </c>
     </row>
     <row r="7">
@@ -442,37 +442,37 @@
         <v>17</v>
       </c>
       <c r="B7" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="3">
-        <v>2076.28</v>
+        <v>562.53</v>
       </c>
       <c r="D7" s="3">
-        <v>1484.33</v>
+        <v>496.29</v>
       </c>
       <c r="E7" s="3">
-        <v>2779.8</v>
+        <v>535.15</v>
       </c>
       <c r="F7" s="3">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="G7" s="3">
-        <v>2814.08</v>
+        <v>-82.1400000000001</v>
       </c>
       <c r="H7" s="3">
-        <v>33.883676575413716</v>
+        <v>-4.867295966437352</v>
       </c>
       <c r="I7" s="3">
-        <v>8305.12</v>
+        <v>1687.59</v>
       </c>
       <c r="J7" s="3">
-        <v>11119.2</v>
+        <v>1605.4499999999998</v>
       </c>
       <c r="K7" s="3">
-        <v>0</v>
+        <v>29.84999999999991</v>
       </c>
       <c r="L7" s="3">
-        <v>0.01</v>
+        <v>562.53</v>
       </c>
     </row>
     <row r="8">
@@ -480,37 +480,37 @@
         <v>18</v>
       </c>
       <c r="B8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="3">
-        <v>385.14</v>
+        <v>7822.16</v>
       </c>
       <c r="D8" s="3">
-        <v>356</v>
+        <v>6234.5</v>
       </c>
       <c r="E8" s="3">
-        <v>445.05</v>
+        <v>6883</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="G8" s="3">
-        <v>119.82000000000005</v>
+        <v>-3725.1399999999994</v>
       </c>
       <c r="H8" s="3">
-        <v>15.55538245832685</v>
+        <v>-15.874302409223706</v>
       </c>
       <c r="I8" s="3">
-        <v>770.28</v>
+        <v>23466.48</v>
       </c>
       <c r="J8" s="3">
-        <v>890.1</v>
+        <v>20649</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>639.5</v>
       </c>
       <c r="L8" s="3">
-        <v>385.14</v>
+        <v>7822.1575</v>
       </c>
     </row>
     <row r="9">
@@ -518,37 +518,37 @@
         <v>19</v>
       </c>
       <c r="B9" s="2">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C9" s="3">
-        <v>497.16</v>
+        <v>2076.28</v>
       </c>
       <c r="D9" s="3">
-        <v>416.05</v>
+        <v>1526.07</v>
       </c>
       <c r="E9" s="3">
-        <v>419.6</v>
+        <v>2867.6</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="G9" s="3">
-        <v>-1240.96</v>
+        <v>3165.279999999999</v>
       </c>
       <c r="H9" s="3">
-        <v>-15.600611473167591</v>
+        <v>38.11239331882018</v>
       </c>
       <c r="I9" s="3">
-        <v>7954.56</v>
+        <v>8305.12</v>
       </c>
       <c r="J9" s="3">
-        <v>6713.6</v>
+        <v>11470.4</v>
       </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>736.3999999999996</v>
       </c>
       <c r="L9" s="3">
-        <v>507.0006</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="10">
@@ -556,37 +556,37 @@
         <v>20</v>
       </c>
       <c r="B10" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3">
-        <v>4138.05</v>
+        <v>62.6</v>
       </c>
       <c r="D10" s="3">
-        <v>3576.1</v>
+        <v>49.91</v>
       </c>
       <c r="E10" s="3">
-        <v>3588.6</v>
+        <v>60.1</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="G10" s="3">
-        <v>-1098.9000000000005</v>
+        <v>-10</v>
       </c>
       <c r="H10" s="3">
-        <v>-13.277993257693849</v>
+        <v>-3.993610223642172</v>
       </c>
       <c r="I10" s="3">
-        <v>8276.1</v>
+        <v>250.4</v>
       </c>
       <c r="J10" s="3">
-        <v>7177.2</v>
+        <v>240.4</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>-0.7599999999999909</v>
       </c>
       <c r="L10" s="3">
-        <v>4145.735</v>
+        <v>62.595</v>
       </c>
     </row>
     <row r="11">
@@ -594,37 +594,37 @@
         <v>21</v>
       </c>
       <c r="B11" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" s="3">
-        <v>562.53</v>
+        <v>101.3</v>
       </c>
       <c r="D11" s="3">
-        <v>496.29</v>
+        <v>71.5</v>
       </c>
       <c r="E11" s="3">
-        <v>531.8</v>
+        <v>107.62</v>
       </c>
       <c r="F11" s="3">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="G11" s="3">
-        <v>-92.19000000000005</v>
+        <v>31.600000000000023</v>
       </c>
       <c r="H11" s="3">
-        <v>-5.462819760723876</v>
+        <v>6.2388943731490665</v>
       </c>
       <c r="I11" s="3">
-        <v>1687.59</v>
+        <v>506.5</v>
       </c>
       <c r="J11" s="3">
-        <v>1595.3999999999999</v>
+        <v>538.1</v>
       </c>
       <c r="K11" s="3">
-        <v>-2.2737367544323206e-13</v>
+        <v>12.700000000000045</v>
       </c>
       <c r="L11" s="3">
-        <v>562.53</v>
+        <v>101.2964</v>
       </c>
     </row>
     <row r="12">
@@ -632,37 +632,37 @@
         <v>22</v>
       </c>
       <c r="B12" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3">
-        <v>720.24</v>
+        <v>1292.42</v>
       </c>
       <c r="D12" s="3">
-        <v>585</v>
+        <v>947.09</v>
       </c>
       <c r="E12" s="3">
-        <v>590.1</v>
+        <v>1138.9</v>
       </c>
       <c r="F12" s="3">
-        <v>0</v>
+        <v>-1.91</v>
       </c>
       <c r="G12" s="3">
-        <v>-1171.2599999999993</v>
+        <v>-1006.04</v>
       </c>
       <c r="H12" s="3">
-        <v>-18.068977007664103</v>
+        <v>-15.56831370607078</v>
       </c>
       <c r="I12" s="3">
-        <v>6482.16</v>
+        <v>6462.1</v>
       </c>
       <c r="J12" s="3">
-        <v>5310.900000000001</v>
+        <v>5694.5</v>
       </c>
       <c r="K12" s="3">
-        <v>9.094947017729282e-13</v>
+        <v>-86.80000000000018</v>
       </c>
       <c r="L12" s="3">
-        <v>720.2433</v>
+        <v>1291.5371</v>
       </c>
     </row>
     <row r="13">
@@ -670,37 +670,37 @@
         <v>23</v>
       </c>
       <c r="B13" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C13" s="3">
-        <v>2453.04</v>
+        <v>94.65</v>
       </c>
       <c r="D13" s="3">
-        <v>1783.43</v>
+        <v>75.7</v>
       </c>
       <c r="E13" s="3">
-        <v>2313.9</v>
+        <v>91.17</v>
       </c>
       <c r="F13" s="3">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="G13" s="3">
-        <v>-278.27999999999975</v>
+        <v>-17.399999999999977</v>
       </c>
       <c r="H13" s="3">
-        <v>-5.672145582624005</v>
+        <v>-3.6767036450079194</v>
       </c>
       <c r="I13" s="3">
-        <v>4906.08</v>
+        <v>473.25</v>
       </c>
       <c r="J13" s="3">
-        <v>4627.8</v>
+        <v>455.85</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>4.900000000000034</v>
       </c>
       <c r="L13" s="3">
-        <v>2566.985</v>
+        <v>94.65</v>
       </c>
     </row>
     <row r="14">
@@ -708,37 +708,37 @@
         <v>24</v>
       </c>
       <c r="B14" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3">
-        <v>882.58</v>
+        <v>378.56</v>
       </c>
       <c r="D14" s="3">
-        <v>741.05</v>
+        <v>219.57</v>
       </c>
       <c r="E14" s="3">
-        <v>756.2</v>
+        <v>362</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="G14" s="3">
-        <v>-2527.5999999999985</v>
+        <v>-82.79999999999995</v>
       </c>
       <c r="H14" s="3">
-        <v>-14.319381812413596</v>
+        <v>-4.374471682163987</v>
       </c>
       <c r="I14" s="3">
-        <v>17651.600000000002</v>
+        <v>1892.8</v>
       </c>
       <c r="J14" s="3">
-        <v>15124</v>
+        <v>1810</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>62.25</v>
       </c>
       <c r="L14" s="3">
-        <v>882.578</v>
+        <v>378.556</v>
       </c>
     </row>
     <row r="15">
@@ -746,37 +746,37 @@
         <v>25</v>
       </c>
       <c r="B15" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3">
-        <v>1386.35</v>
+        <v>1862.35</v>
       </c>
       <c r="D15" s="3">
-        <v>1218.1</v>
+        <v>1627</v>
       </c>
       <c r="E15" s="3">
-        <v>1233.8</v>
+        <v>1647</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="G15" s="3">
-        <v>-1220.3999999999996</v>
+        <v>-1507.4500000000007</v>
       </c>
       <c r="H15" s="3">
-        <v>-11.003714790637282</v>
+        <v>-11.563347383681915</v>
       </c>
       <c r="I15" s="3">
-        <v>11090.8</v>
+        <v>13036.449999999999</v>
       </c>
       <c r="J15" s="3">
-        <v>9870.4</v>
+        <v>11529</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>106.39999999999964</v>
       </c>
       <c r="L15" s="3">
-        <v>1386.3513</v>
+        <v>1857.9286</v>
       </c>
     </row>
     <row r="16">
@@ -784,37 +784,37 @@
         <v>26</v>
       </c>
       <c r="B16" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3">
-        <v>66.49</v>
+        <v>1394.66</v>
       </c>
       <c r="D16" s="3">
-        <v>52.46</v>
+        <v>1086</v>
       </c>
       <c r="E16" s="3">
-        <v>61.87</v>
+        <v>1203.9</v>
       </c>
       <c r="F16" s="3">
-        <v>0</v>
+        <v>9.78</v>
       </c>
       <c r="G16" s="3">
-        <v>-55.440000000000055</v>
+        <v>-1716.039999999999</v>
       </c>
       <c r="H16" s="3">
-        <v>-6.948413295232374</v>
+        <v>-17.577658456438936</v>
       </c>
       <c r="I16" s="3">
-        <v>797.8799999999999</v>
+        <v>9762.62</v>
       </c>
       <c r="J16" s="3">
-        <v>742.4399999999999</v>
+        <v>8427.300000000001</v>
       </c>
       <c r="K16" s="3">
-        <v>-1.1368683772161603e-13</v>
+        <v>966.5000000000009</v>
       </c>
       <c r="L16" s="3">
-        <v>66.4942</v>
+        <v>1394.6589</v>
       </c>
     </row>
     <row r="17">
@@ -822,37 +822,37 @@
         <v>27</v>
       </c>
       <c r="B17" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C17" s="3">
-        <v>62.6</v>
+        <v>1386.35</v>
       </c>
       <c r="D17" s="3">
-        <v>49.91</v>
+        <v>1200.4</v>
       </c>
       <c r="E17" s="3">
-        <v>59.46</v>
+        <v>1212.7</v>
       </c>
       <c r="F17" s="3">
-        <v>0</v>
+        <v>0.56</v>
       </c>
       <c r="G17" s="3">
-        <v>-12.560000000000002</v>
+        <v>-1389.199999999999</v>
       </c>
       <c r="H17" s="3">
-        <v>-5.01597444089457</v>
+        <v>-12.52569697406859</v>
       </c>
       <c r="I17" s="3">
-        <v>250.4</v>
+        <v>11090.8</v>
       </c>
       <c r="J17" s="3">
-        <v>237.84</v>
+        <v>9701.6</v>
       </c>
       <c r="K17" s="3">
-        <v>0</v>
+        <v>54.399999999999636</v>
       </c>
       <c r="L17" s="3">
-        <v>62.595</v>
+        <v>1386.3513</v>
       </c>
     </row>
     <row r="18">
@@ -860,37 +860,37 @@
         <v>28</v>
       </c>
       <c r="B18" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C18" s="3">
-        <v>363.15</v>
+        <v>720.24</v>
       </c>
       <c r="D18" s="3">
-        <v>288.75</v>
+        <v>555.3</v>
       </c>
       <c r="E18" s="3">
-        <v>294.7</v>
+        <v>576.65</v>
       </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="G18" s="3">
-        <v>-1095.1999999999998</v>
+        <v>-1292.3100000000004</v>
       </c>
       <c r="H18" s="3">
-        <v>-18.848960484648213</v>
+        <v>-19.936410085527054</v>
       </c>
       <c r="I18" s="3">
-        <v>5810.4</v>
+        <v>6482.16</v>
       </c>
       <c r="J18" s="3">
-        <v>4715.2</v>
+        <v>5189.849999999999</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>150.29999999999927</v>
       </c>
       <c r="L18" s="3">
-        <v>363.1456</v>
+        <v>720.2433</v>
       </c>
     </row>
     <row r="19">
@@ -898,37 +898,37 @@
         <v>29</v>
       </c>
       <c r="B19" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C19" s="3">
-        <v>99.92</v>
+        <v>974.31</v>
       </c>
       <c r="D19" s="3">
-        <v>71.5</v>
+        <v>788</v>
       </c>
       <c r="E19" s="3">
-        <v>109.38</v>
+        <v>844.6</v>
       </c>
       <c r="F19" s="3">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="G19" s="3">
-        <v>37.839999999999975</v>
+        <v>-1167.3900000000003</v>
       </c>
       <c r="H19" s="3">
-        <v>9.467574059247392</v>
+        <v>-13.31301125925014</v>
       </c>
       <c r="I19" s="3">
-        <v>399.68</v>
+        <v>8768.789999999999</v>
       </c>
       <c r="J19" s="3">
-        <v>437.52</v>
+        <v>7601.400000000001</v>
       </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>481.0500000000002</v>
       </c>
       <c r="L19" s="3">
-        <v>99.9178</v>
+        <v>974.3111</v>
       </c>
     </row>
     <row r="20">
@@ -939,34 +939,34 @@
         <v>9</v>
       </c>
       <c r="C20" s="3">
-        <v>974.31</v>
+        <v>452.11</v>
       </c>
       <c r="D20" s="3">
-        <v>830.05</v>
+        <v>365.9</v>
       </c>
       <c r="E20" s="3">
-        <v>832.7</v>
+        <v>419</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>11.01</v>
       </c>
       <c r="G20" s="3">
-        <v>-1274.4900000000007</v>
+        <v>-297.9899999999998</v>
       </c>
       <c r="H20" s="3">
-        <v>-14.534388438997864</v>
+        <v>-7.323438986087451</v>
       </c>
       <c r="I20" s="3">
-        <v>8768.789999999999</v>
+        <v>4068.9900000000002</v>
       </c>
       <c r="J20" s="3">
-        <v>7494.3</v>
+        <v>3771</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>373.9499999999998</v>
       </c>
       <c r="L20" s="3">
-        <v>974.3111</v>
+        <v>452.1056</v>
       </c>
     </row>
     <row r="21">
@@ -974,37 +974,37 @@
         <v>31</v>
       </c>
       <c r="B21" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C21" s="3">
-        <v>1292.42</v>
+        <v>89.58</v>
       </c>
       <c r="D21" s="3">
-        <v>947.09</v>
+        <v>70.46</v>
       </c>
       <c r="E21" s="3">
-        <v>1195.4</v>
+        <v>76.49</v>
       </c>
       <c r="F21" s="3">
-        <v>0</v>
+        <v>7.88</v>
       </c>
       <c r="G21" s="3">
-        <v>-679.1399999999994</v>
+        <v>-130.89999999999998</v>
       </c>
       <c r="H21" s="3">
-        <v>-7.506847619194993</v>
+        <v>-14.61263674927439</v>
       </c>
       <c r="I21" s="3">
-        <v>9046.94</v>
+        <v>895.8</v>
       </c>
       <c r="J21" s="3">
-        <v>8367.800000000001</v>
+        <v>764.9</v>
       </c>
       <c r="K21" s="3">
-        <v>1.8189894035458565e-12</v>
+        <v>55.89999999999998</v>
       </c>
       <c r="L21" s="3">
-        <v>1291.5371</v>
+        <v>89.578</v>
       </c>
     </row>
     <row r="22">
@@ -1012,37 +1012,37 @@
         <v>32</v>
       </c>
       <c r="B22" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C22" s="3">
-        <v>7822.16</v>
+        <v>66.49</v>
       </c>
       <c r="D22" s="3">
-        <v>6234.5</v>
+        <v>52.46</v>
       </c>
       <c r="E22" s="3">
-        <v>6947</v>
+        <v>60.18</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="G22" s="3">
-        <v>-3500.6399999999994</v>
+        <v>-75.72000000000003</v>
       </c>
       <c r="H22" s="3">
-        <v>-11.188213997156794</v>
+        <v>-9.490148894570618</v>
       </c>
       <c r="I22" s="3">
-        <v>31288.64</v>
+        <v>797.8799999999999</v>
       </c>
       <c r="J22" s="3">
-        <v>27788</v>
+        <v>722.16</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>15.959999999999923</v>
       </c>
       <c r="L22" s="3">
-        <v>7822.1575</v>
+        <v>66.4942</v>
       </c>
     </row>
     <row r="23">
@@ -1050,37 +1050,37 @@
         <v>33</v>
       </c>
       <c r="B23" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C23" s="3">
-        <v>94.65</v>
+        <v>434.6</v>
       </c>
       <c r="D23" s="3">
-        <v>75.6</v>
+        <v>394</v>
       </c>
       <c r="E23" s="3">
-        <v>90.29</v>
+        <v>420.35</v>
       </c>
       <c r="F23" s="3">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="G23" s="3">
-        <v>-21.799999999999955</v>
+        <v>-185.25</v>
       </c>
       <c r="H23" s="3">
-        <v>-4.6064447966191135</v>
+        <v>-3.2788771283939253</v>
       </c>
       <c r="I23" s="3">
-        <v>473.25</v>
+        <v>5649.8</v>
       </c>
       <c r="J23" s="3">
-        <v>451.45000000000005</v>
+        <v>5464.55</v>
       </c>
       <c r="K23" s="3">
-        <v>5.684341886080802e-14</v>
+        <v>248.30000000000018</v>
       </c>
       <c r="L23" s="3">
-        <v>94.65</v>
+        <v>434.5992</v>
       </c>
     </row>
     <row r="24">
@@ -1088,37 +1088,37 @@
         <v>34</v>
       </c>
       <c r="B24" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C24" s="3">
-        <v>290.34</v>
+        <v>778.04</v>
       </c>
       <c r="D24" s="3">
-        <v>318</v>
+        <v>538.85</v>
       </c>
       <c r="E24" s="3">
-        <v>384.55</v>
+        <v>577.1</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>6.64</v>
       </c>
       <c r="G24" s="3">
-        <v>94.21000000000004</v>
+        <v>-2612.2200000000003</v>
       </c>
       <c r="H24" s="3">
-        <v>32.448164221257855</v>
+        <v>-25.826435658835024</v>
       </c>
       <c r="I24" s="3">
-        <v>290.34</v>
+        <v>10114.52</v>
       </c>
       <c r="J24" s="3">
-        <v>384.55</v>
+        <v>7502.3</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>467.35000000000036</v>
       </c>
       <c r="L24" s="3">
-        <v>83.73</v>
+        <v>778.0431</v>
       </c>
     </row>
     <row r="25">
@@ -1126,37 +1126,37 @@
         <v>35</v>
       </c>
       <c r="B25" s="2">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C25" s="3">
-        <v>624.49</v>
+        <v>497.16</v>
       </c>
       <c r="D25" s="3">
-        <v>473.95</v>
+        <v>408</v>
       </c>
       <c r="E25" s="3">
-        <v>481.55</v>
+        <v>414.95</v>
       </c>
       <c r="F25" s="3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="G25" s="3">
-        <v>-4431.139999999998</v>
+        <v>-1315.3600000000006</v>
       </c>
       <c r="H25" s="3">
-        <v>-22.889077487229567</v>
+        <v>-16.535924048596033</v>
       </c>
       <c r="I25" s="3">
-        <v>19359.19</v>
+        <v>7954.56</v>
       </c>
       <c r="J25" s="3">
-        <v>14928.050000000001</v>
+        <v>6639.2</v>
       </c>
       <c r="K25" s="3">
-        <v>1.8189894035458565e-12</v>
+        <v>72</v>
       </c>
       <c r="L25" s="3">
-        <v>776.8819</v>
+        <v>507.0006</v>
       </c>
     </row>
     <row r="26">
@@ -1164,37 +1164,37 @@
         <v>36</v>
       </c>
       <c r="B26" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C26" s="3">
-        <v>356.05</v>
+        <v>363.15</v>
       </c>
       <c r="D26" s="3">
-        <v>310.55</v>
+        <v>287</v>
       </c>
       <c r="E26" s="3">
-        <v>318.45</v>
+        <v>291.7</v>
       </c>
       <c r="F26" s="3">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="G26" s="3">
-        <v>-714.3999999999996</v>
+        <v>-1143.1999999999998</v>
       </c>
       <c r="H26" s="3">
-        <v>-10.560314562561434</v>
+        <v>-19.67506539997246</v>
       </c>
       <c r="I26" s="3">
-        <v>6764.95</v>
+        <v>5810.4</v>
       </c>
       <c r="J26" s="3">
-        <v>6050.55</v>
+        <v>4667.2</v>
       </c>
       <c r="K26" s="3">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="L26" s="3">
-        <v>356.0532</v>
+        <v>363.1456</v>
       </c>
     </row>
     <row r="27">
@@ -1202,37 +1202,37 @@
         <v>37</v>
       </c>
       <c r="B27" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C27" s="3">
-        <v>48.69</v>
+        <v>356.05</v>
       </c>
       <c r="D27" s="3">
-        <v>38.19</v>
+        <v>304.05</v>
       </c>
       <c r="E27" s="3">
-        <v>40.82</v>
+        <v>322.1</v>
       </c>
       <c r="F27" s="3">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="G27" s="3">
-        <v>-196.75</v>
+        <v>-645.0499999999993</v>
       </c>
       <c r="H27" s="3">
-        <v>-16.16348326144999</v>
+        <v>-9.535177643589373</v>
       </c>
       <c r="I27" s="3">
-        <v>1217.25</v>
+        <v>6764.95</v>
       </c>
       <c r="J27" s="3">
-        <v>1020.5</v>
+        <v>6119.900000000001</v>
       </c>
       <c r="K27" s="3">
-        <v>0</v>
+        <v>323.0000000000009</v>
       </c>
       <c r="L27" s="3">
-        <v>48.6852</v>
+        <v>356.0532</v>
       </c>
     </row>
     <row r="28">
@@ -1240,37 +1240,37 @@
         <v>38</v>
       </c>
       <c r="B28" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C28" s="3">
-        <v>452.11</v>
+        <v>882.58</v>
       </c>
       <c r="D28" s="3">
-        <v>393.9</v>
+        <v>726.65</v>
       </c>
       <c r="E28" s="3">
-        <v>398.45</v>
+        <v>742.25</v>
       </c>
       <c r="F28" s="3">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="G28" s="3">
-        <v>-482.94000000000005</v>
+        <v>-2806.5999999999985</v>
       </c>
       <c r="H28" s="3">
-        <v>-11.868792992855722</v>
+        <v>-15.899975073081182</v>
       </c>
       <c r="I28" s="3">
-        <v>4068.9900000000002</v>
+        <v>17651.600000000002</v>
       </c>
       <c r="J28" s="3">
-        <v>3586.0499999999997</v>
+        <v>14845</v>
       </c>
       <c r="K28" s="3">
-        <v>-4.547473508864641e-13</v>
+        <v>214</v>
       </c>
       <c r="L28" s="3">
-        <v>452.1056</v>
+        <v>882.578</v>
       </c>
     </row>
     <row r="29">
@@ -1278,37 +1278,37 @@
         <v>39</v>
       </c>
       <c r="B29" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C29" s="3">
-        <v>778.04</v>
+        <v>48.69</v>
       </c>
       <c r="D29" s="3">
-        <v>563.25</v>
+        <v>38.19</v>
       </c>
       <c r="E29" s="3">
-        <v>567.5</v>
+        <v>41.12</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="G29" s="3">
-        <v>-2737.0200000000004</v>
+        <v>-189.25</v>
       </c>
       <c r="H29" s="3">
-        <v>-27.06030538275667</v>
+        <v>-15.547340316286713</v>
       </c>
       <c r="I29" s="3">
-        <v>10114.52</v>
+        <v>1217.25</v>
       </c>
       <c r="J29" s="3">
-        <v>7377.5</v>
+        <v>1028</v>
       </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L29" s="3">
-        <v>778.0431</v>
+        <v>48.6852</v>
       </c>
     </row>
     <row r="30">
@@ -1316,37 +1316,37 @@
         <v>40</v>
       </c>
       <c r="B30" s="2">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C30" s="3">
-        <v>378.56</v>
+        <v>614.8</v>
       </c>
       <c r="D30" s="3">
-        <v>226.2</v>
+        <v>444</v>
       </c>
       <c r="E30" s="3">
-        <v>361.25</v>
+        <v>490.95</v>
       </c>
       <c r="F30" s="3">
-        <v>0</v>
+        <v>9.98</v>
       </c>
       <c r="G30" s="3">
-        <v>-86.54999999999995</v>
+        <v>-4116.25</v>
       </c>
       <c r="H30" s="3">
-        <v>-4.572590870667791</v>
+        <v>-23.087126735916367</v>
       </c>
       <c r="I30" s="3">
-        <v>1892.8</v>
+        <v>17829.199999999997</v>
       </c>
       <c r="J30" s="3">
-        <v>1806.25</v>
+        <v>14237.55</v>
       </c>
       <c r="K30" s="3">
-        <v>0</v>
+        <v>1440.949999999999</v>
       </c>
       <c r="L30" s="3">
-        <v>378.556</v>
+        <v>757.9555</v>
       </c>
     </row>
     <row r="31">
@@ -1363,25 +1363,25 @@
         <v>363</v>
       </c>
       <c r="E31" s="3">
-        <v>649.4</v>
+        <v>677.2</v>
       </c>
       <c r="F31" s="3">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="G31" s="3">
-        <v>12702.419999999998</v>
+        <v>14203.620000000003</v>
       </c>
       <c r="H31" s="3">
-        <v>56.795518748340044</v>
+        <v>63.50773836830288</v>
       </c>
       <c r="I31" s="3">
         <v>22365.18</v>
       </c>
       <c r="J31" s="3">
-        <v>35067.6</v>
+        <v>36568.8</v>
       </c>
       <c r="K31" s="3">
-        <v>0</v>
+        <v>1209.6000000000058</v>
       </c>
       <c r="L31" s="3">
         <v>414.1652</v>
@@ -1398,25 +1398,25 @@
         <v>0.77</v>
       </c>
       <c r="D32" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="E32" s="3">
         <v>0.24</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0.25</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-1246.96</v>
+        <v>-1270.94</v>
       </c>
       <c r="H32" s="3">
-        <v>-67.53246753246754</v>
+        <v>-68.83116883116884</v>
       </c>
       <c r="I32" s="3">
         <v>1846.46</v>
       </c>
       <c r="J32" s="3">
-        <v>599.5</v>
+        <v>575.52</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>

--- a/portfolio_holdings.xlsx
+++ b/portfolio_holdings.xlsx
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t>P&amp;L DAY</t>
+  </si>
+  <si>
+    <t>WEIGHTED AVG RATE</t>
   </si>
   <si>
     <t>ALEMBICLTD</t>
@@ -193,6 +196,7 @@
     <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -229,10 +233,13 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2">
         <v>10</v>
@@ -244,30 +251,33 @@
         <v>70.46</v>
       </c>
       <c r="E2" s="3">
-        <v>85.73</v>
+        <v>85.8</v>
       </c>
       <c r="F2" s="4">
-        <v>0.0125</v>
+        <v>0.013300000000000001</v>
       </c>
       <c r="G2" s="3">
-        <v>-39.799999999999955</v>
+        <v>-39.10000000000002</v>
       </c>
       <c r="H2" s="4">
-        <v>-0.04436517668041463</v>
+        <v>-0.043584884628246605</v>
       </c>
       <c r="I2" s="3">
         <v>897.0999999999999</v>
       </c>
       <c r="J2" s="3">
-        <v>857.3000000000001</v>
+        <v>858</v>
       </c>
       <c r="K2" s="3">
-        <v>10.600000000000023</v>
+        <v>11.299999999999955</v>
+      </c>
+      <c r="L2" s="3">
+        <v>89.71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2">
         <v>13</v>
@@ -279,30 +289,33 @@
         <v>394</v>
       </c>
       <c r="E3" s="3">
-        <v>437.1</v>
+        <v>438.5</v>
       </c>
       <c r="F3" s="4">
-        <v>0.006999999999999999</v>
+        <v>0.0103</v>
       </c>
       <c r="G3" s="3">
-        <v>33.02000000000044</v>
+        <v>51.220000000000255</v>
       </c>
       <c r="H3" s="4">
-        <v>0.005844992636229827</v>
+        <v>0.009066642120765878</v>
       </c>
       <c r="I3" s="3">
         <v>5649.28</v>
       </c>
       <c r="J3" s="3">
-        <v>5682.3</v>
+        <v>5700.5</v>
       </c>
       <c r="K3" s="3">
-        <v>39.650000000000546</v>
+        <v>57.850000000000364</v>
+      </c>
+      <c r="L3" s="3">
+        <v>434.5615</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2">
         <v>1</v>
@@ -314,30 +327,33 @@
         <v>1016.1</v>
       </c>
       <c r="E4" s="3">
-        <v>1351.8</v>
+        <v>1349.3</v>
       </c>
       <c r="F4" s="4">
-        <v>0.0085</v>
+        <v>0.0066</v>
       </c>
       <c r="G4" s="3">
-        <v>291.39999999999986</v>
+        <v>288.89999999999986</v>
       </c>
       <c r="H4" s="4">
-        <v>0.2748019615239531</v>
+        <v>0.2724443606186343</v>
       </c>
       <c r="I4" s="3">
         <v>1060.4</v>
       </c>
       <c r="J4" s="3">
-        <v>1351.8</v>
+        <v>1349.3</v>
       </c>
       <c r="K4" s="3">
-        <v>11.399999999999864</v>
+        <v>8.899999999999864</v>
+      </c>
+      <c r="L4" s="3">
+        <v>880.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2">
         <v>7</v>
@@ -349,30 +365,33 @@
         <v>1597</v>
       </c>
       <c r="E5" s="3">
-        <v>1795.5</v>
+        <v>1799.6</v>
       </c>
       <c r="F5" s="4">
-        <v>0.015700000000000002</v>
+        <v>0.018000000000000002</v>
       </c>
       <c r="G5" s="3">
-        <v>-468.9300000000003</v>
+        <v>-440.2300000000014</v>
       </c>
       <c r="H5" s="4">
-        <v>-0.03596797835156164</v>
+        <v>-0.03376662425033165</v>
       </c>
       <c r="I5" s="3">
         <v>13037.43</v>
       </c>
       <c r="J5" s="3">
-        <v>12568.5</v>
+        <v>12597.199999999999</v>
       </c>
       <c r="K5" s="3">
-        <v>194.60000000000036</v>
+        <v>223.29999999999927</v>
+      </c>
+      <c r="L5" s="3">
+        <v>1858.0657</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2">
         <v>7</v>
@@ -384,30 +403,33 @@
         <v>1086</v>
       </c>
       <c r="E6" s="3">
-        <v>1351.2</v>
+        <v>1346.4</v>
       </c>
       <c r="F6" s="4">
-        <v>0.0194</v>
+        <v>0.0158</v>
       </c>
       <c r="G6" s="3">
-        <v>419.22999999999956</v>
+        <v>385.630000000001</v>
       </c>
       <c r="H6" s="4">
-        <v>0.04637925827260684</v>
+        <v>0.04266210282581266</v>
       </c>
       <c r="I6" s="3">
         <v>9039.17</v>
       </c>
       <c r="J6" s="3">
-        <v>9458.4</v>
+        <v>9424.800000000001</v>
       </c>
       <c r="K6" s="3">
-        <v>179.89999999999964</v>
+        <v>146.3000000000011</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1450.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2">
         <v>4</v>
@@ -419,30 +441,33 @@
         <v>1784.18</v>
       </c>
       <c r="E7" s="3">
-        <v>3248.1</v>
+        <v>3259.7</v>
       </c>
       <c r="F7" s="4">
-        <v>-0.0029</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="G7" s="3">
-        <v>4687.76</v>
+        <v>4734.16</v>
       </c>
       <c r="H7" s="4">
-        <v>0.5644747996300864</v>
+        <v>0.5700620376078915</v>
       </c>
       <c r="I7" s="3">
         <v>8304.64</v>
       </c>
       <c r="J7" s="3">
-        <v>12992.4</v>
+        <v>13038.8</v>
       </c>
       <c r="K7" s="3">
-        <v>-37.20000000000073</v>
+        <v>9.199999999998909</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2">
         <v>2</v>
@@ -454,30 +479,33 @@
         <v>368.65</v>
       </c>
       <c r="E8" s="3">
-        <v>453.75</v>
+        <v>453.2</v>
       </c>
       <c r="F8" s="4">
-        <v>-0.0008</v>
+        <v>-0.002</v>
       </c>
       <c r="G8" s="3">
-        <v>137.22000000000003</v>
+        <v>136.12</v>
       </c>
       <c r="H8" s="4">
-        <v>0.17814301293036303</v>
+        <v>0.17671496079347768</v>
       </c>
       <c r="I8" s="3">
         <v>770.28</v>
       </c>
       <c r="J8" s="3">
-        <v>907.5</v>
+        <v>906.4</v>
       </c>
       <c r="K8" s="3">
-        <v>-0.7000000000000455</v>
+        <v>-1.8000000000000682</v>
+      </c>
+      <c r="L8" s="3">
+        <v>385.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2">
         <v>21</v>
@@ -489,30 +517,33 @@
         <v>403.35</v>
       </c>
       <c r="E9" s="3">
-        <v>429.95</v>
+        <v>431.65</v>
       </c>
       <c r="F9" s="4">
-        <v>0.0013</v>
+        <v>0.0052</v>
       </c>
       <c r="G9" s="3">
-        <v>-1019.9700000000012</v>
+        <v>-984.2700000000004</v>
       </c>
       <c r="H9" s="4">
-        <v>-0.10150045975089872</v>
+        <v>-0.09794783917077661</v>
       </c>
       <c r="I9" s="3">
         <v>10048.92</v>
       </c>
       <c r="J9" s="3">
-        <v>9028.949999999999</v>
+        <v>9064.65</v>
       </c>
       <c r="K9" s="3">
-        <v>11.549999999999272</v>
+        <v>47.25</v>
+      </c>
+      <c r="L9" s="3">
+        <v>486.0286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
@@ -524,30 +555,33 @@
         <v>3479.1</v>
       </c>
       <c r="E10" s="3">
-        <v>4108</v>
+        <v>4105.5</v>
       </c>
       <c r="F10" s="4">
-        <v>0.018600000000000002</v>
+        <v>0.018000000000000002</v>
       </c>
       <c r="G10" s="3">
-        <v>-59.92000000000007</v>
+        <v>-64.92000000000007</v>
       </c>
       <c r="H10" s="4">
-        <v>-0.007240282651354782</v>
+        <v>-0.007844445088884386</v>
       </c>
       <c r="I10" s="3">
         <v>8275.92</v>
       </c>
       <c r="J10" s="3">
-        <v>8216</v>
+        <v>8211</v>
       </c>
       <c r="K10" s="3">
-        <v>150.19999999999982</v>
+        <v>145.19999999999982</v>
+      </c>
+      <c r="L10" s="3">
+        <v>4146</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2">
         <v>3</v>
@@ -559,30 +593,33 @@
         <v>509.06</v>
       </c>
       <c r="E11" s="3">
-        <v>549.3</v>
+        <v>555.75</v>
       </c>
       <c r="F11" s="4">
-        <v>0.006500000000000001</v>
+        <v>0.0183</v>
       </c>
       <c r="G11" s="3">
-        <v>-39.36000000000013</v>
+        <v>-20.00999999999999</v>
       </c>
       <c r="H11" s="4">
-        <v>-0.023327762170619895</v>
+        <v>-0.01185946445716724</v>
       </c>
       <c r="I11" s="3">
         <v>1687.2599999999998</v>
       </c>
       <c r="J11" s="3">
-        <v>1647.8999999999999</v>
+        <v>1667.25</v>
       </c>
       <c r="K11" s="3">
-        <v>10.649999999999864</v>
+        <v>30</v>
+      </c>
+      <c r="L11" s="3">
+        <v>562.42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2">
         <v>11</v>
@@ -594,30 +631,33 @@
         <v>555.3</v>
       </c>
       <c r="E12" s="3">
-        <v>628.65</v>
+        <v>628.9</v>
       </c>
       <c r="F12" s="4">
-        <v>0.0154</v>
+        <v>0.0158</v>
       </c>
       <c r="G12" s="3">
-        <v>-733.2600000000002</v>
+        <v>-730.5100000000002</v>
       </c>
       <c r="H12" s="4">
-        <v>-0.09587090650213577</v>
+        <v>-0.0955113546475673</v>
       </c>
       <c r="I12" s="3">
         <v>7648.41</v>
       </c>
       <c r="J12" s="3">
-        <v>6915.15</v>
+        <v>6917.9</v>
       </c>
       <c r="K12" s="3">
-        <v>105.04999999999927</v>
+        <v>107.79999999999927</v>
+      </c>
+      <c r="L12" s="3">
+        <v>695.3082</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2">
         <v>22</v>
@@ -629,30 +669,33 @@
         <v>726.65</v>
       </c>
       <c r="E13" s="3">
-        <v>806.6</v>
+        <v>810.2</v>
       </c>
       <c r="F13" s="4">
-        <v>0.011200000000000002</v>
+        <v>0.015700000000000002</v>
       </c>
       <c r="G13" s="3">
-        <v>-1382.9199999999983</v>
+        <v>-1303.7199999999975</v>
       </c>
       <c r="H13" s="4">
-        <v>-0.07229774802751122</v>
+        <v>-0.06815724702689012</v>
       </c>
       <c r="I13" s="3">
         <v>19128.120000000003</v>
       </c>
       <c r="J13" s="3">
-        <v>17745.2</v>
+        <v>17824.4</v>
       </c>
       <c r="K13" s="3">
-        <v>195.79999999999927</v>
+        <v>275</v>
+      </c>
+      <c r="L13" s="3">
+        <v>869.4605</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2">
         <v>9</v>
@@ -664,30 +707,33 @@
         <v>1187.6</v>
       </c>
       <c r="E14" s="3">
-        <v>1309.5</v>
+        <v>1313.4</v>
       </c>
       <c r="F14" s="4">
-        <v>0.022000000000000002</v>
+        <v>0.025099999999999997</v>
       </c>
       <c r="G14" s="3">
-        <v>-503.72999999999956</v>
+        <v>-468.6299999999992</v>
       </c>
       <c r="H14" s="4">
-        <v>-0.0409895493859257</v>
+        <v>-0.038133389968289244</v>
       </c>
       <c r="I14" s="3">
         <v>12289.23</v>
       </c>
       <c r="J14" s="3">
-        <v>11785.5</v>
+        <v>11820.6</v>
       </c>
       <c r="K14" s="3">
-        <v>253.79999999999927</v>
+        <v>288.89999999999964</v>
+      </c>
+      <c r="L14" s="3">
+        <v>1365.4678</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2">
         <v>12</v>
@@ -699,30 +745,33 @@
         <v>56.56</v>
       </c>
       <c r="E15" s="3">
-        <v>66.13</v>
+        <v>65.97</v>
       </c>
       <c r="F15" s="4">
-        <v>0.013000000000000001</v>
+        <v>0.0106</v>
       </c>
       <c r="G15" s="3">
-        <v>-5.040000000000077</v>
+        <v>-6.960000000000036</v>
       </c>
       <c r="H15" s="4">
-        <v>-0.00631104432757335</v>
+        <v>-0.008715251690458349</v>
       </c>
       <c r="I15" s="3">
         <v>798.5999999999999</v>
       </c>
       <c r="J15" s="3">
-        <v>793.56</v>
+        <v>791.64</v>
       </c>
       <c r="K15" s="3">
-        <v>10.199999999999932</v>
+        <v>8.279999999999973</v>
+      </c>
+      <c r="L15" s="3">
+        <v>66.5508</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2">
         <v>12</v>
@@ -734,30 +783,33 @@
         <v>141.74</v>
       </c>
       <c r="E16" s="3">
-        <v>157.66</v>
+        <v>158</v>
       </c>
       <c r="F16" s="4">
-        <v>0.0165</v>
+        <v>0.0187</v>
       </c>
       <c r="G16" s="3">
-        <v>104.16000000000008</v>
+        <v>108.24000000000001</v>
       </c>
       <c r="H16" s="4">
-        <v>0.058262854074372455</v>
+        <v>0.06054503960263124</v>
       </c>
       <c r="I16" s="3">
         <v>1787.7599999999998</v>
       </c>
       <c r="J16" s="3">
-        <v>1891.92</v>
+        <v>1896</v>
       </c>
       <c r="K16" s="3">
-        <v>30.720000000000027</v>
+        <v>34.799999999999955</v>
+      </c>
+      <c r="L16" s="3">
+        <v>148.9833</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17" s="2">
         <v>23</v>
@@ -769,30 +821,33 @@
         <v>287</v>
       </c>
       <c r="E17" s="3">
-        <v>303.25</v>
+        <v>304.9</v>
       </c>
       <c r="F17" s="4">
-        <v>0.0008</v>
+        <v>0.0063</v>
       </c>
       <c r="G17" s="3">
-        <v>-905.0500000000002</v>
+        <v>-867.1000000000004</v>
       </c>
       <c r="H17" s="4">
-        <v>-0.11485697606538241</v>
+        <v>-0.11004086398131935</v>
       </c>
       <c r="I17" s="3">
         <v>7879.8</v>
       </c>
       <c r="J17" s="3">
-        <v>6974.75</v>
+        <v>7012.7</v>
       </c>
       <c r="K17" s="3">
-        <v>5.75</v>
+        <v>43.69999999999982</v>
+      </c>
+      <c r="L17" s="3">
+        <v>342.5957</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="2">
         <v>9</v>
@@ -804,30 +859,33 @@
         <v>74.67</v>
       </c>
       <c r="E18" s="3">
-        <v>119</v>
+        <v>119.29</v>
       </c>
       <c r="F18" s="4">
-        <v>0.018000000000000002</v>
+        <v>0.0204</v>
       </c>
       <c r="G18" s="3">
-        <v>147.69000000000005</v>
+        <v>150.30000000000018</v>
       </c>
       <c r="H18" s="4">
-        <v>0.1599571108295156</v>
+        <v>0.16278389706599103</v>
       </c>
       <c r="I18" s="3">
         <v>923.3100000000001</v>
       </c>
       <c r="J18" s="3">
-        <v>1071</v>
+        <v>1073.6100000000001</v>
       </c>
       <c r="K18" s="3">
-        <v>18.90000000000009</v>
+        <v>21.51000000000022</v>
+      </c>
+      <c r="L18" s="3">
+        <v>102.5916</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" s="2">
         <v>9</v>
@@ -839,30 +897,33 @@
         <v>788</v>
       </c>
       <c r="E19" s="3">
-        <v>923.7</v>
+        <v>923.95</v>
       </c>
       <c r="F19" s="4">
-        <v>0.011399999999999999</v>
+        <v>0.011699999999999999</v>
       </c>
       <c r="G19" s="3">
-        <v>-455.4899999999998</v>
+        <v>-453.2399999999998</v>
       </c>
       <c r="H19" s="4">
-        <v>-0.051944452997505906</v>
+        <v>-0.05168786115302109</v>
       </c>
       <c r="I19" s="3">
         <v>8768.789999999999</v>
       </c>
       <c r="J19" s="3">
-        <v>8313.300000000001</v>
+        <v>8315.550000000001</v>
       </c>
       <c r="K19" s="3">
-        <v>94.05000000000109</v>
+        <v>96.30000000000109</v>
+      </c>
+      <c r="L19" s="3">
+        <v>974.3089</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20" s="2">
         <v>3</v>
@@ -874,30 +935,33 @@
         <v>76.32</v>
       </c>
       <c r="E20" s="3">
-        <v>92.45</v>
+        <v>92.49</v>
       </c>
       <c r="F20" s="4">
-        <v>0.0028000000000000004</v>
+        <v>0.0033</v>
       </c>
       <c r="G20" s="3">
-        <v>-3</v>
+        <v>-2.8800000000000523</v>
       </c>
       <c r="H20" s="4">
-        <v>-0.010700909577314071</v>
+        <v>-0.010272873194221694</v>
       </c>
       <c r="I20" s="3">
         <v>280.35</v>
       </c>
       <c r="J20" s="3">
-        <v>277.35</v>
+        <v>277.46999999999997</v>
       </c>
       <c r="K20" s="3">
-        <v>0.7800000000000296</v>
+        <v>0.8999999999999773</v>
+      </c>
+      <c r="L20" s="3">
+        <v>96.7633</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" s="2">
         <v>11</v>
@@ -909,30 +973,33 @@
         <v>346.3</v>
       </c>
       <c r="E21" s="3">
-        <v>398.8</v>
+        <v>408</v>
       </c>
       <c r="F21" s="4">
-        <v>-0.0073</v>
+        <v>0.015600000000000001</v>
       </c>
       <c r="G21" s="3">
-        <v>32.67000000000007</v>
+        <v>133.8699999999999</v>
       </c>
       <c r="H21" s="4">
-        <v>0.007503221079756478</v>
+        <v>0.030745522067554227</v>
       </c>
       <c r="I21" s="3">
         <v>4354.13</v>
       </c>
       <c r="J21" s="3">
-        <v>4386.8</v>
+        <v>4488</v>
       </c>
       <c r="K21" s="3">
-        <v>-32.44999999999982</v>
+        <v>68.75</v>
+      </c>
+      <c r="L21" s="3">
+        <v>377.0455</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" s="2">
         <v>29</v>
@@ -944,30 +1011,33 @@
         <v>444</v>
       </c>
       <c r="E22" s="3">
-        <v>527.4</v>
+        <v>532.05</v>
       </c>
       <c r="F22" s="4">
-        <v>0.026000000000000002</v>
+        <v>0.035</v>
       </c>
       <c r="G22" s="3">
-        <v>-1588.9099999999999</v>
+        <v>-1454.0599999999995</v>
       </c>
       <c r="H22" s="4">
-        <v>-0.09411017021934417</v>
+        <v>-0.08612308696473656</v>
       </c>
       <c r="I22" s="3">
         <v>16883.510000000002</v>
       </c>
       <c r="J22" s="3">
-        <v>15294.599999999999</v>
+        <v>15429.449999999999</v>
       </c>
       <c r="K22" s="3">
-        <v>387.1499999999978</v>
+        <v>521.9999999999982</v>
+      </c>
+      <c r="L22" s="3">
+        <v>796.0379</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="2">
         <v>19</v>
@@ -979,30 +1049,33 @@
         <v>304.05</v>
       </c>
       <c r="E23" s="3">
-        <v>348.3</v>
+        <v>348.95</v>
       </c>
       <c r="F23" s="4">
-        <v>0.0043</v>
+        <v>0.0062</v>
       </c>
       <c r="G23" s="3">
-        <v>-148.57999999999993</v>
+        <v>-136.22999999999956</v>
       </c>
       <c r="H23" s="4">
-        <v>-0.021958890261709527</v>
+        <v>-0.0201336628102886</v>
       </c>
       <c r="I23" s="3">
         <v>6766.28</v>
       </c>
       <c r="J23" s="3">
-        <v>6617.7</v>
+        <v>6630.05</v>
       </c>
       <c r="K23" s="3">
-        <v>28.5</v>
+        <v>40.850000000000364</v>
+      </c>
+      <c r="L23" s="3">
+        <v>356.1221</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2">
         <v>27</v>
@@ -1014,30 +1087,33 @@
         <v>38.19</v>
       </c>
       <c r="E24" s="3">
-        <v>44.94</v>
+        <v>44.99</v>
       </c>
       <c r="F24" s="4">
-        <v>0.0161</v>
+        <v>0.0172</v>
       </c>
       <c r="G24" s="3">
-        <v>-83.97000000000003</v>
+        <v>-82.61999999999989</v>
       </c>
       <c r="H24" s="4">
-        <v>-0.06472424557752345</v>
+        <v>-0.06368366285119659</v>
       </c>
       <c r="I24" s="3">
         <v>1297.35</v>
       </c>
       <c r="J24" s="3">
-        <v>1213.3799999999999</v>
+        <v>1214.73</v>
       </c>
       <c r="K24" s="3">
-        <v>19.169999999999845</v>
+        <v>20.519999999999982</v>
+      </c>
+      <c r="L24" s="3">
+        <v>48.0485</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" s="2">
         <v>15</v>
@@ -1049,30 +1125,33 @@
         <v>365.9</v>
       </c>
       <c r="E25" s="3">
-        <v>480.4</v>
+        <v>482.35</v>
       </c>
       <c r="F25" s="4">
-        <v>0.013999999999999999</v>
+        <v>0.0182</v>
       </c>
       <c r="G25" s="3">
-        <v>636.4499999999998</v>
+        <v>665.6999999999998</v>
       </c>
       <c r="H25" s="4">
-        <v>0.09687878165171128</v>
+        <v>0.10133114140237913</v>
       </c>
       <c r="I25" s="3">
         <v>6569.55</v>
       </c>
       <c r="J25" s="3">
-        <v>7206</v>
+        <v>7235.25</v>
       </c>
       <c r="K25" s="3">
-        <v>99.75</v>
+        <v>129</v>
+      </c>
+      <c r="L25" s="3">
+        <v>437.972</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" s="2">
         <v>13</v>
@@ -1084,30 +1163,33 @@
         <v>538.85</v>
       </c>
       <c r="E26" s="3">
-        <v>646</v>
+        <v>647.4</v>
       </c>
       <c r="F26" s="4">
-        <v>0.0144</v>
+        <v>0.0166</v>
       </c>
       <c r="G26" s="3">
-        <v>-1716.5200000000004</v>
+        <v>-1698.3200000000015</v>
       </c>
       <c r="H26" s="4">
-        <v>-0.16970849827772355</v>
+        <v>-0.16790910493033792</v>
       </c>
       <c r="I26" s="3">
         <v>10114.52</v>
       </c>
       <c r="J26" s="3">
-        <v>8398</v>
+        <v>8416.199999999999</v>
       </c>
       <c r="K26" s="3">
-        <v>118.95000000000073</v>
+        <v>137.14999999999964</v>
+      </c>
+      <c r="L26" s="3">
+        <v>778.0408</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27" s="2">
         <v>54</v>
@@ -1119,30 +1201,33 @@
         <v>368.15</v>
       </c>
       <c r="E27" s="3">
-        <v>735.9</v>
+        <v>738.75</v>
       </c>
       <c r="F27" s="4">
-        <v>-0.0015</v>
+        <v>0.0024</v>
       </c>
       <c r="G27" s="3">
-        <v>17373.96</v>
+        <v>17527.86</v>
       </c>
       <c r="H27" s="4">
-        <v>0.7768495267529457</v>
+        <v>0.7837309252462815</v>
       </c>
       <c r="I27" s="3">
         <v>22364.640000000003</v>
       </c>
       <c r="J27" s="3">
-        <v>39738.6</v>
+        <v>39892.5</v>
       </c>
       <c r="K27" s="3">
-        <v>-59.400000000001455</v>
+        <v>94.5</v>
+      </c>
+      <c r="L27" s="3">
+        <v>414.163</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="2">
         <v>2398</v>
@@ -1173,6 +1258,9 @@
       </c>
       <c r="K28" s="3">
         <v>71.94000000000005</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0.7732</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio_holdings.xlsx
+++ b/portfolio_holdings.xlsx
@@ -101,9 +101,6 @@
   </si>
   <si>
     <t>NSDL</t>
-  </si>
-  <si>
-    <t>PGINVIT</t>
   </si>
   <si>
     <t>POONAWALLA</t>
@@ -251,25 +248,25 @@
         <v>70.46</v>
       </c>
       <c r="E2" s="3">
-        <v>85.8</v>
+        <v>84.64</v>
       </c>
       <c r="F2" s="4">
-        <v>0.013300000000000001</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3">
-        <v>-39.10000000000002</v>
+        <v>-50.700000000000045</v>
       </c>
       <c r="H2" s="4">
-        <v>-0.043584884628246605</v>
+        <v>-0.05651543863560367</v>
       </c>
       <c r="I2" s="3">
         <v>897.0999999999999</v>
       </c>
       <c r="J2" s="3">
-        <v>858</v>
+        <v>846.4</v>
       </c>
       <c r="K2" s="3">
-        <v>11.299999999999955</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3">
         <v>89.71</v>
@@ -289,25 +286,25 @@
         <v>394</v>
       </c>
       <c r="E3" s="3">
-        <v>438.5</v>
+        <v>441</v>
       </c>
       <c r="F3" s="4">
-        <v>0.0103</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>51.220000000000255</v>
+        <v>83.72000000000025</v>
       </c>
       <c r="H3" s="4">
-        <v>0.009066642120765878</v>
+        <v>0.014819587628866027</v>
       </c>
       <c r="I3" s="3">
         <v>5649.28</v>
       </c>
       <c r="J3" s="3">
-        <v>5700.5</v>
+        <v>5733</v>
       </c>
       <c r="K3" s="3">
-        <v>57.850000000000364</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3">
         <v>434.5615</v>
@@ -327,25 +324,25 @@
         <v>1016.1</v>
       </c>
       <c r="E4" s="3">
-        <v>1349.3</v>
+        <v>1339.8</v>
       </c>
       <c r="F4" s="4">
-        <v>0.0066</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3">
-        <v>288.89999999999986</v>
+        <v>279.39999999999986</v>
       </c>
       <c r="H4" s="4">
-        <v>0.2724443606186343</v>
+        <v>0.2634854771784231</v>
       </c>
       <c r="I4" s="3">
         <v>1060.4</v>
       </c>
       <c r="J4" s="3">
-        <v>1349.3</v>
+        <v>1339.8</v>
       </c>
       <c r="K4" s="3">
-        <v>8.899999999999864</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3">
         <v>880.48</v>
@@ -365,25 +362,25 @@
         <v>1597</v>
       </c>
       <c r="E5" s="3">
-        <v>1799.6</v>
+        <v>1788.3</v>
       </c>
       <c r="F5" s="4">
-        <v>0.018000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3">
-        <v>-440.2300000000014</v>
+        <v>-519.3299999999999</v>
       </c>
       <c r="H5" s="4">
-        <v>-0.03376662425033165</v>
+        <v>-0.0398337709195754</v>
       </c>
       <c r="I5" s="3">
         <v>13037.43</v>
       </c>
       <c r="J5" s="3">
-        <v>12597.199999999999</v>
+        <v>12518.1</v>
       </c>
       <c r="K5" s="3">
-        <v>223.29999999999927</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3">
         <v>1858.0657</v>
@@ -403,25 +400,25 @@
         <v>1086</v>
       </c>
       <c r="E6" s="3">
-        <v>1346.4</v>
+        <v>1332.8</v>
       </c>
       <c r="F6" s="4">
-        <v>0.0158</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3">
-        <v>385.630000000001</v>
+        <v>290.4300000000003</v>
       </c>
       <c r="H6" s="4">
-        <v>0.04266210282581266</v>
+        <v>0.03213016239322861</v>
       </c>
       <c r="I6" s="3">
         <v>9039.17</v>
       </c>
       <c r="J6" s="3">
-        <v>9424.800000000001</v>
+        <v>9329.6</v>
       </c>
       <c r="K6" s="3">
-        <v>146.3000000000011</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3">
         <v>1450.74</v>
@@ -438,28 +435,28 @@
         <v>2076.16</v>
       </c>
       <c r="D7" s="3">
-        <v>1784.18</v>
+        <v>1802.53</v>
       </c>
       <c r="E7" s="3">
-        <v>3259.7</v>
+        <v>3303.6</v>
       </c>
       <c r="F7" s="4">
-        <v>0.0007000000000000001</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3">
-        <v>4734.16</v>
+        <v>4909.76</v>
       </c>
       <c r="H7" s="4">
-        <v>0.5700620376078915</v>
+        <v>0.591206843403206</v>
       </c>
       <c r="I7" s="3">
         <v>8304.64</v>
       </c>
       <c r="J7" s="3">
-        <v>13038.8</v>
+        <v>13214.4</v>
       </c>
       <c r="K7" s="3">
-        <v>9.199999999998909</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3">
         <v>0.01</v>
@@ -479,25 +476,25 @@
         <v>368.65</v>
       </c>
       <c r="E8" s="3">
-        <v>453.2</v>
+        <v>435.1</v>
       </c>
       <c r="F8" s="4">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
-        <v>136.12</v>
+        <v>99.92000000000007</v>
       </c>
       <c r="H8" s="4">
-        <v>0.17671496079347768</v>
+        <v>0.1297190631977983</v>
       </c>
       <c r="I8" s="3">
         <v>770.28</v>
       </c>
       <c r="J8" s="3">
-        <v>906.4</v>
+        <v>870.2</v>
       </c>
       <c r="K8" s="3">
-        <v>-1.8000000000000682</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
         <v>385.14</v>
@@ -517,25 +514,25 @@
         <v>403.35</v>
       </c>
       <c r="E9" s="3">
-        <v>431.65</v>
+        <v>424.75</v>
       </c>
       <c r="F9" s="4">
-        <v>0.0052</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3">
-        <v>-984.2700000000004</v>
+        <v>-1129.17</v>
       </c>
       <c r="H9" s="4">
-        <v>-0.09794783917077661</v>
+        <v>-0.11236729917244839</v>
       </c>
       <c r="I9" s="3">
         <v>10048.92</v>
       </c>
       <c r="J9" s="3">
-        <v>9064.65</v>
+        <v>8919.75</v>
       </c>
       <c r="K9" s="3">
-        <v>47.25</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3">
         <v>486.0286</v>
@@ -555,25 +552,25 @@
         <v>3479.1</v>
       </c>
       <c r="E10" s="3">
-        <v>4105.5</v>
+        <v>4099.9</v>
       </c>
       <c r="F10" s="4">
-        <v>0.018000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
-        <v>-64.92000000000007</v>
+        <v>-76.1200000000008</v>
       </c>
       <c r="H10" s="4">
-        <v>-0.007844445088884386</v>
+        <v>-0.009197768948950788</v>
       </c>
       <c r="I10" s="3">
         <v>8275.92</v>
       </c>
       <c r="J10" s="3">
-        <v>8211</v>
+        <v>8199.8</v>
       </c>
       <c r="K10" s="3">
-        <v>145.19999999999982</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3">
         <v>4146</v>
@@ -593,25 +590,25 @@
         <v>509.06</v>
       </c>
       <c r="E11" s="3">
-        <v>555.75</v>
+        <v>550.65</v>
       </c>
       <c r="F11" s="4">
-        <v>0.0183</v>
+        <v>0</v>
       </c>
       <c r="G11" s="3">
-        <v>-20.00999999999999</v>
+        <v>-35.31000000000017</v>
       </c>
       <c r="H11" s="4">
-        <v>-0.01185946445716724</v>
+        <v>-0.020927420788734503</v>
       </c>
       <c r="I11" s="3">
         <v>1687.2599999999998</v>
       </c>
       <c r="J11" s="3">
-        <v>1667.25</v>
+        <v>1651.9499999999998</v>
       </c>
       <c r="K11" s="3">
-        <v>30</v>
+        <v>-2.2737367544323206e-13</v>
       </c>
       <c r="L11" s="3">
         <v>562.42</v>
@@ -631,25 +628,25 @@
         <v>555.3</v>
       </c>
       <c r="E12" s="3">
-        <v>628.9</v>
+        <v>614.8</v>
       </c>
       <c r="F12" s="4">
-        <v>0.0158</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>-730.5100000000002</v>
+        <v>-885.6100000000006</v>
       </c>
       <c r="H12" s="4">
-        <v>-0.0955113546475673</v>
+        <v>-0.11579007924522883</v>
       </c>
       <c r="I12" s="3">
         <v>7648.41</v>
       </c>
       <c r="J12" s="3">
-        <v>6917.9</v>
+        <v>6762.799999999999</v>
       </c>
       <c r="K12" s="3">
-        <v>107.79999999999927</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="L12" s="3">
         <v>695.3082</v>
@@ -660,37 +657,37 @@
         <v>23</v>
       </c>
       <c r="B13" s="2">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C13" s="3">
-        <v>869.46</v>
+        <v>844.69</v>
       </c>
       <c r="D13" s="3">
         <v>726.65</v>
       </c>
       <c r="E13" s="3">
-        <v>810.2</v>
+        <v>794.7</v>
       </c>
       <c r="F13" s="4">
-        <v>0.015700000000000002</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3">
-        <v>-1303.7199999999975</v>
+        <v>-1699.6599999999962</v>
       </c>
       <c r="H13" s="4">
-        <v>-0.06815724702689012</v>
+        <v>-0.05918147486059962</v>
       </c>
       <c r="I13" s="3">
-        <v>19128.120000000003</v>
+        <v>28719.460000000003</v>
       </c>
       <c r="J13" s="3">
-        <v>17824.4</v>
+        <v>27019.800000000003</v>
       </c>
       <c r="K13" s="3">
-        <v>275</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="L13" s="3">
-        <v>869.4605</v>
+        <v>844.6903</v>
       </c>
     </row>
     <row r="14">
@@ -707,25 +704,25 @@
         <v>1187.6</v>
       </c>
       <c r="E14" s="3">
-        <v>1313.4</v>
+        <v>1351.1</v>
       </c>
       <c r="F14" s="4">
-        <v>0.025099999999999997</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>-468.6299999999992</v>
+        <v>-129.32999999999993</v>
       </c>
       <c r="H14" s="4">
-        <v>-0.038133389968289244</v>
+        <v>-0.010523848931137258</v>
       </c>
       <c r="I14" s="3">
         <v>12289.23</v>
       </c>
       <c r="J14" s="3">
-        <v>11820.6</v>
+        <v>12159.9</v>
       </c>
       <c r="K14" s="3">
-        <v>288.89999999999964</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3">
         <v>1365.4678</v>
@@ -742,28 +739,28 @@
         <v>66.55</v>
       </c>
       <c r="D15" s="3">
-        <v>56.56</v>
+        <v>57.32</v>
       </c>
       <c r="E15" s="3">
-        <v>65.97</v>
+        <v>64.86</v>
       </c>
       <c r="F15" s="4">
-        <v>0.0106</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>-6.960000000000036</v>
+        <v>-20.280000000000086</v>
       </c>
       <c r="H15" s="4">
-        <v>-0.008715251690458349</v>
+        <v>-0.02539444027047344</v>
       </c>
       <c r="I15" s="3">
         <v>798.5999999999999</v>
       </c>
       <c r="J15" s="3">
-        <v>791.64</v>
+        <v>778.3199999999999</v>
       </c>
       <c r="K15" s="3">
-        <v>8.279999999999973</v>
+        <v>-1.1368683772161603e-13</v>
       </c>
       <c r="L15" s="3">
         <v>66.5508</v>
@@ -783,25 +780,25 @@
         <v>141.74</v>
       </c>
       <c r="E16" s="3">
-        <v>158</v>
+        <v>162.25</v>
       </c>
       <c r="F16" s="4">
-        <v>0.0187</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3">
-        <v>108.24000000000001</v>
+        <v>159.24</v>
       </c>
       <c r="H16" s="4">
-        <v>0.06054503960263124</v>
+        <v>0.08907235870586656</v>
       </c>
       <c r="I16" s="3">
         <v>1787.7599999999998</v>
       </c>
       <c r="J16" s="3">
-        <v>1896</v>
+        <v>1947</v>
       </c>
       <c r="K16" s="3">
-        <v>34.799999999999955</v>
+        <v>0</v>
       </c>
       <c r="L16" s="3">
         <v>148.9833</v>
@@ -821,25 +818,25 @@
         <v>287</v>
       </c>
       <c r="E17" s="3">
-        <v>304.9</v>
+        <v>298.65</v>
       </c>
       <c r="F17" s="4">
-        <v>0.0063</v>
+        <v>0</v>
       </c>
       <c r="G17" s="3">
-        <v>-867.1000000000004</v>
+        <v>-1010.8500000000004</v>
       </c>
       <c r="H17" s="4">
-        <v>-0.11004086398131935</v>
+        <v>-0.12828371278458847</v>
       </c>
       <c r="I17" s="3">
         <v>7879.8</v>
       </c>
       <c r="J17" s="3">
-        <v>7012.7</v>
+        <v>6868.95</v>
       </c>
       <c r="K17" s="3">
-        <v>43.69999999999982</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3">
         <v>342.5957</v>
@@ -859,25 +856,25 @@
         <v>74.67</v>
       </c>
       <c r="E18" s="3">
-        <v>119.29</v>
+        <v>119.11</v>
       </c>
       <c r="F18" s="4">
-        <v>0.0204</v>
+        <v>0</v>
       </c>
       <c r="G18" s="3">
-        <v>150.30000000000018</v>
+        <v>148.68000000000006</v>
       </c>
       <c r="H18" s="4">
-        <v>0.16278389706599103</v>
+        <v>0.16102934009162692</v>
       </c>
       <c r="I18" s="3">
         <v>923.3100000000001</v>
       </c>
       <c r="J18" s="3">
-        <v>1073.6100000000001</v>
+        <v>1071.99</v>
       </c>
       <c r="K18" s="3">
-        <v>21.51000000000022</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3">
         <v>102.5916</v>
@@ -897,25 +894,25 @@
         <v>788</v>
       </c>
       <c r="E19" s="3">
-        <v>923.95</v>
+        <v>911.25</v>
       </c>
       <c r="F19" s="4">
-        <v>0.011699999999999999</v>
+        <v>-0.0158</v>
       </c>
       <c r="G19" s="3">
-        <v>-453.2399999999998</v>
+        <v>-567.5400000000009</v>
       </c>
       <c r="H19" s="4">
-        <v>-0.05168786115302109</v>
+        <v>-0.06472272685284981</v>
       </c>
       <c r="I19" s="3">
         <v>8768.789999999999</v>
       </c>
       <c r="J19" s="3">
-        <v>8315.550000000001</v>
+        <v>8201.25</v>
       </c>
       <c r="K19" s="3">
-        <v>96.30000000000109</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3">
         <v>974.3089</v>
@@ -926,37 +923,37 @@
         <v>30</v>
       </c>
       <c r="B20" s="2">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C20" s="3">
-        <v>93.45</v>
+        <v>394.15</v>
       </c>
       <c r="D20" s="3">
-        <v>76.32</v>
+        <v>346.75</v>
       </c>
       <c r="E20" s="3">
-        <v>92.49</v>
+        <v>408.75</v>
       </c>
       <c r="F20" s="4">
-        <v>0.0033</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-2.8800000000000523</v>
+        <v>379.60000000000036</v>
       </c>
       <c r="H20" s="4">
-        <v>-0.010272873194221694</v>
+        <v>0.03704173537993154</v>
       </c>
       <c r="I20" s="3">
-        <v>280.35</v>
+        <v>10247.9</v>
       </c>
       <c r="J20" s="3">
-        <v>277.46999999999997</v>
+        <v>10627.5</v>
       </c>
       <c r="K20" s="3">
-        <v>0.8999999999999773</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>96.7633</v>
+        <v>386.2077</v>
       </c>
     </row>
     <row r="21">
@@ -964,37 +961,37 @@
         <v>31</v>
       </c>
       <c r="B21" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C21" s="3">
-        <v>395.83</v>
+        <v>515.29</v>
       </c>
       <c r="D21" s="3">
-        <v>346.3</v>
+        <v>444</v>
       </c>
       <c r="E21" s="3">
-        <v>408</v>
+        <v>533.2</v>
       </c>
       <c r="F21" s="4">
-        <v>0.015600000000000001</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>133.8699999999999</v>
+        <v>250.7400000000007</v>
       </c>
       <c r="H21" s="4">
-        <v>0.030745522067554227</v>
+        <v>0.034757127054668345</v>
       </c>
       <c r="I21" s="3">
-        <v>4354.13</v>
+        <v>7214.0599999999995</v>
       </c>
       <c r="J21" s="3">
-        <v>4488</v>
+        <v>7464.800000000001</v>
       </c>
       <c r="K21" s="3">
-        <v>68.75</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="L21" s="3">
-        <v>377.0455</v>
+        <v>1076.2657</v>
       </c>
     </row>
     <row r="22">
@@ -1002,37 +999,37 @@
         <v>32</v>
       </c>
       <c r="B22" s="2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C22" s="3">
-        <v>582.19</v>
+        <v>356.12</v>
       </c>
       <c r="D22" s="3">
-        <v>444</v>
+        <v>304.05</v>
       </c>
       <c r="E22" s="3">
-        <v>532.05</v>
+        <v>347</v>
       </c>
       <c r="F22" s="4">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3">
-        <v>-1454.0599999999995</v>
+        <v>-173.27999999999975</v>
       </c>
       <c r="H22" s="4">
-        <v>-0.08612308696473656</v>
+        <v>-0.02560934516455124</v>
       </c>
       <c r="I22" s="3">
-        <v>16883.510000000002</v>
+        <v>6766.28</v>
       </c>
       <c r="J22" s="3">
-        <v>15429.449999999999</v>
+        <v>6593</v>
       </c>
       <c r="K22" s="3">
-        <v>521.9999999999982</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3">
-        <v>796.0379</v>
+        <v>356.1221</v>
       </c>
     </row>
     <row r="23">
@@ -1040,37 +1037,37 @@
         <v>33</v>
       </c>
       <c r="B23" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C23" s="3">
-        <v>356.12</v>
+        <v>48.05</v>
       </c>
       <c r="D23" s="3">
-        <v>304.05</v>
+        <v>38.19</v>
       </c>
       <c r="E23" s="3">
-        <v>348.95</v>
+        <v>45.86</v>
       </c>
       <c r="F23" s="4">
-        <v>0.0062</v>
+        <v>0</v>
       </c>
       <c r="G23" s="3">
-        <v>-136.22999999999956</v>
+        <v>-59.12999999999988</v>
       </c>
       <c r="H23" s="4">
-        <v>-0.0201336628102886</v>
+        <v>-0.045577523413111255</v>
       </c>
       <c r="I23" s="3">
-        <v>6766.28</v>
+        <v>1297.35</v>
       </c>
       <c r="J23" s="3">
-        <v>6630.05</v>
+        <v>1238.22</v>
       </c>
       <c r="K23" s="3">
-        <v>40.850000000000364</v>
+        <v>0</v>
       </c>
       <c r="L23" s="3">
-        <v>356.1221</v>
+        <v>48.0485</v>
       </c>
     </row>
     <row r="24">
@@ -1078,37 +1075,37 @@
         <v>34</v>
       </c>
       <c r="B24" s="2">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C24" s="3">
-        <v>48.05</v>
+        <v>437.97</v>
       </c>
       <c r="D24" s="3">
-        <v>38.19</v>
+        <v>365.9</v>
       </c>
       <c r="E24" s="3">
-        <v>44.99</v>
+        <v>461.75</v>
       </c>
       <c r="F24" s="4">
-        <v>0.0172</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>-82.61999999999989</v>
+        <v>356.6999999999998</v>
       </c>
       <c r="H24" s="4">
-        <v>-0.06368366285119659</v>
+        <v>0.0542959563440418</v>
       </c>
       <c r="I24" s="3">
-        <v>1297.35</v>
+        <v>6569.55</v>
       </c>
       <c r="J24" s="3">
-        <v>1214.73</v>
+        <v>6926.25</v>
       </c>
       <c r="K24" s="3">
-        <v>20.519999999999982</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>48.0485</v>
+        <v>437.972</v>
       </c>
     </row>
     <row r="25">
@@ -1116,37 +1113,37 @@
         <v>35</v>
       </c>
       <c r="B25" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C25" s="3">
-        <v>437.97</v>
+        <v>778.04</v>
       </c>
       <c r="D25" s="3">
-        <v>365.9</v>
+        <v>538.85</v>
       </c>
       <c r="E25" s="3">
-        <v>482.35</v>
+        <v>713.2</v>
       </c>
       <c r="F25" s="4">
-        <v>0.0182</v>
+        <v>0</v>
       </c>
       <c r="G25" s="3">
-        <v>665.6999999999998</v>
+        <v>-842.9200000000001</v>
       </c>
       <c r="H25" s="4">
-        <v>0.10133114140237913</v>
+        <v>-0.08333761760320807</v>
       </c>
       <c r="I25" s="3">
-        <v>6569.55</v>
+        <v>10114.52</v>
       </c>
       <c r="J25" s="3">
-        <v>7235.25</v>
+        <v>9271.6</v>
       </c>
       <c r="K25" s="3">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>437.972</v>
+        <v>778.0408</v>
       </c>
     </row>
     <row r="26">
@@ -1154,37 +1151,37 @@
         <v>36</v>
       </c>
       <c r="B26" s="2">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C26" s="3">
-        <v>778.04</v>
+        <v>414.16</v>
       </c>
       <c r="D26" s="3">
-        <v>538.85</v>
+        <v>368.6</v>
       </c>
       <c r="E26" s="3">
-        <v>647.4</v>
+        <v>752.55</v>
       </c>
       <c r="F26" s="4">
-        <v>0.0166</v>
+        <v>0</v>
       </c>
       <c r="G26" s="3">
-        <v>-1698.3200000000015</v>
+        <v>18273.059999999998</v>
       </c>
       <c r="H26" s="4">
-        <v>-0.16790910493033792</v>
+        <v>0.81705138110875</v>
       </c>
       <c r="I26" s="3">
-        <v>10114.52</v>
+        <v>22364.640000000003</v>
       </c>
       <c r="J26" s="3">
-        <v>8416.199999999999</v>
+        <v>40637.7</v>
       </c>
       <c r="K26" s="3">
-        <v>137.14999999999964</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3">
-        <v>778.0408</v>
+        <v>414.163</v>
       </c>
     </row>
     <row r="27">
@@ -1192,74 +1189,36 @@
         <v>37</v>
       </c>
       <c r="B27" s="2">
-        <v>54</v>
+        <v>2398</v>
       </c>
       <c r="C27" s="3">
-        <v>414.16</v>
+        <v>0.77</v>
       </c>
       <c r="D27" s="3">
-        <v>368.15</v>
+        <v>0.23</v>
       </c>
       <c r="E27" s="3">
-        <v>738.75</v>
+        <v>0.35</v>
       </c>
       <c r="F27" s="4">
-        <v>0.0024</v>
+        <v>0.0294</v>
       </c>
       <c r="G27" s="3">
-        <v>17527.86</v>
+        <v>-1007.1600000000001</v>
       </c>
       <c r="H27" s="4">
-        <v>0.7837309252462815</v>
+        <v>-0.5454545454545455</v>
       </c>
       <c r="I27" s="3">
-        <v>22364.640000000003</v>
+        <v>1846.46</v>
       </c>
       <c r="J27" s="3">
-        <v>39892.5</v>
+        <v>839.3</v>
       </c>
       <c r="K27" s="3">
-        <v>94.5</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>414.163</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="2">
-        <v>2398</v>
-      </c>
-      <c r="C28" s="3">
-        <v>0.77</v>
-      </c>
-      <c r="D28" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="E28" s="3">
-        <v>0.34</v>
-      </c>
-      <c r="F28" s="4">
-        <v>0.0968</v>
-      </c>
-      <c r="G28" s="3">
-        <v>-1031.1399999999999</v>
-      </c>
-      <c r="H28" s="4">
-        <v>-0.5584415584415584</v>
-      </c>
-      <c r="I28" s="3">
-        <v>1846.46</v>
-      </c>
-      <c r="J28" s="3">
-        <v>815.32</v>
-      </c>
-      <c r="K28" s="3">
-        <v>71.94000000000005</v>
-      </c>
-      <c r="L28" s="3">
         <v>0.7732</v>
       </c>
     </row>
